--- a/dspackagefolder/template/checklist/STATISTICS_CHECKLIST.xlsx
+++ b/dspackagefolder/template/checklist/STATISTICS_CHECKLIST.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajim\Desktop\NonPHD_Muizdeen\INTERVIEWS\dspackage\dspackagefolder\template\checklist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DECC3DD-11BF-425F-9A92-608345225A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E184FC93-0D06-40B1-8210-1D005292F87F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,12 +25,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>check for absence or presence of heteroscadascity</t>
   </si>
   <si>
     <t>obtain what data types comparison is being made</t>
+  </si>
+  <si>
+    <t>CHECKS ON STATISTICAL ANALYSIS</t>
+  </si>
+  <si>
+    <t>Normal distribution has been checked</t>
+  </si>
+  <si>
+    <t>Parametric test used for parametric data</t>
   </si>
 </sst>
 </file>
@@ -83,6 +92,16 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E1959320-1271-4181-8E4D-8BE57638A9FA}" name="Table1" displayName="Table1" ref="A1:A1048576" totalsRowShown="0">
+  <autoFilter ref="A1:A1048576" xr:uid="{E1959320-1271-4181-8E4D-8BE57638A9FA}"/>
+  <tableColumns count="1">
+    <tableColumn id="1" xr3:uid="{A381E6AB-202A-4D96-B7A1-5DC1984E65BB}" name="CHECKS ON STATISTICAL ANALYSIS"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -348,12 +367,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="55.1796875" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+    </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
@@ -364,7 +388,20 @@
         <v>1</v>
       </c>
     </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/dspackagefolder/template/checklist/STATISTICS_CHECKLIST.xlsx
+++ b/dspackagefolder/template/checklist/STATISTICS_CHECKLIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajim\Desktop\NonPHD_Muizdeen\INTERVIEWS\dspackage\dspackagefolder\template\checklist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E184FC93-0D06-40B1-8210-1D005292F87F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199C6808-1652-49C8-92B9-2B7256A73E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>check for absence or presence of heteroscadascity</t>
   </si>
@@ -40,6 +40,9 @@
   </si>
   <si>
     <t>Parametric test used for parametric data</t>
+  </si>
+  <si>
+    <t>Sampling bias has been checked and corrected</t>
   </si>
 </sst>
 </file>
@@ -367,7 +370,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="55.1796875" customWidth="1"/>
@@ -398,6 +401,11 @@
         <v>4</v>
       </c>
     </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/dspackagefolder/template/checklist/STATISTICS_CHECKLIST.xlsx
+++ b/dspackagefolder/template/checklist/STATISTICS_CHECKLIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajim\Desktop\NonPHD_Muizdeen\INTERVIEWS\dspackage\dspackagefolder\template\checklist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199C6808-1652-49C8-92B9-2B7256A73E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C351DAD8-7071-4865-9713-B00E874720DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>check for absence or presence of heteroscadascity</t>
   </si>
@@ -43,6 +43,9 @@
   </si>
   <si>
     <t>Sampling bias has been checked and corrected</t>
+  </si>
+  <si>
+    <t>Bootstrapping steps for CI has been done</t>
   </si>
 </sst>
 </file>
@@ -370,7 +373,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="55.1796875" customWidth="1"/>
@@ -406,6 +409,11 @@
         <v>5</v>
       </c>
     </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
